--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -88,12 +88,6 @@
     <t>later</t>
   </si>
   <si>
-    <t>Max?</t>
-  </si>
-  <si>
-    <t>Kai?</t>
-  </si>
-  <si>
     <t>Tatjana</t>
   </si>
   <si>
@@ -259,9 +253,6 @@
     <t>5.9 statistical Errors</t>
   </si>
   <si>
-    <t>5.10 specialities</t>
-  </si>
-  <si>
     <t>5.10.1 Vapor-Liquid equilibrium</t>
   </si>
   <si>
@@ -302,6 +293,18 @@
   </si>
   <si>
     <t>10. Error-Messages</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Tatjana / Simon</t>
+  </si>
+  <si>
+    <t>5.10 Special Features</t>
+  </si>
+  <si>
+    <t>Andreas / Simon</t>
   </si>
 </sst>
 </file>
@@ -369,12 +372,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -387,8 +384,14 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -704,25 +707,25 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -742,15 +745,15 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>34</v>
+      <c r="E8" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -761,7 +764,7 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -769,43 +772,43 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -813,19 +816,19 @@
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -835,7 +838,7 @@
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
@@ -843,47 +846,47 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>51</v>
+      </c>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
@@ -891,65 +894,65 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>27</v>
+        <v>57</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="G33" s="12"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="G34" s="12"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" s="7"/>
+        <v>61</v>
+      </c>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>22</v>
@@ -957,7 +960,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>20</v>
@@ -965,33 +968,33 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G42" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C43" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G43" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C44" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G44" s="12"/>
+        <v>69</v>
+      </c>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G45" s="4"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C46" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>22</v>
@@ -999,49 +1002,49 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C48" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="11" t="s">
-        <v>78</v>
+      <c r="C51" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C52" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s">
         <v>21</v>
@@ -1049,187 +1052,187 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C56" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="6" t="s">
         <v>18</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="9" t="s">
-        <v>85</v>
+      <c r="C59" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
-        <v>45</v>
+      <c r="A61" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D61" s="5"/>
       <c r="G61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D62" s="5"/>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D63" s="5"/>
-      <c r="E63" s="6"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D64" s="5"/>
-      <c r="E64" s="6"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D65" s="5"/>
-      <c r="E65" s="6"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="6"/>
+      <c r="E66" s="10"/>
       <c r="F66" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="E67" s="6"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6" t="s">
-        <v>29</v>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D71" s="5"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D72" s="5"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D73" s="5"/>
-      <c r="E73" s="6"/>
+      <c r="E73" s="10"/>
       <c r="F73" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D74" s="5"/>
-      <c r="E74" s="6"/>
+      <c r="E74" s="10"/>
       <c r="F74" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -1237,17 +1240,17 @@
         <v>19</v>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="6"/>
+      <c r="E75" s="10"/>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D76" s="5"/>
-      <c r="E76" s="6"/>
+      <c r="E76" s="10"/>
       <c r="F76" t="s">
         <v>20</v>
       </c>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="99">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -305,13 +305,19 @@
   </si>
   <si>
     <t>Andreas / Simon</t>
+  </si>
+  <si>
+    <t>Bearbeiter</t>
+  </si>
+  <si>
+    <t>Stand</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,11 +338,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <strike/>
       <sz val="9"/>
-      <color rgb="FF444444"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,7 +378,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -355,11 +386,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -372,26 +412,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -694,578 +779,821 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:H76"/>
+  <dimension ref="A2:K76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="20" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="24"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="24"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="24"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="24"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="24"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F19" s="24"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20" s="24"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" s="26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="F24" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" s="26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="F32" s="27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F33" s="27"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F34" s="27"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F35" s="27"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F36" s="27"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G38" t="s">
+      <c r="F38" s="26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C39" s="2" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G39" t="s">
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="28" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C40" s="2" t="s">
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="2" t="s">
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="28" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="29" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="2" t="s">
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G43" s="11"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="2" t="s">
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G44" s="11"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14" t="s">
         <v>73</v>
       </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="28"/>
       <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C46" s="2" t="s">
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C47" s="2" t="s">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="28" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C48" s="2" t="s">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="28" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="2" t="s">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="28" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C50" s="2" t="s">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G50" t="s">
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="28" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="9" t="s">
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="15" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C52" s="2" t="s">
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="13"/>
+      <c r="B53" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G53" t="s">
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C55" s="2" t="s">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G55" t="s">
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="28" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C56" s="2" t="s">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G56" t="s">
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="28" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="6" t="s">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G57" t="s">
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H57" t="s">
+      <c r="G57" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="2" t="s">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G58" t="s">
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="28" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="7" t="s">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G59" t="s">
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="28" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="C60" s="4"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="F61" s="25"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G60" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="G61" s="5"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="3" t="s">
+      <c r="F62" s="30"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="7"/>
+      <c r="B63" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="10"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="3" t="s">
+      <c r="C63" s="9"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="30"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="7"/>
+      <c r="B64" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="10"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="30"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="3" t="s">
+      <c r="A65" s="7"/>
+      <c r="B65" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="10"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="30"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="3" t="s">
+      <c r="A66" s="7"/>
+      <c r="B66" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="10"/>
-      <c r="F66" t="s">
+      <c r="C66" s="9"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="30" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="10"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="30"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B68" s="2" t="s">
+      <c r="A68" s="8"/>
+      <c r="B68" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10" t="s">
+      <c r="C68" s="9"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B69" s="2" t="s">
+      <c r="A69" s="8"/>
+      <c r="B69" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="31"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B70" s="2" t="s">
+      <c r="A70" s="8"/>
+      <c r="B70" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="31"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B71" s="2" t="s">
+      <c r="A71" s="8"/>
+      <c r="B71" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="31"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B72" s="2" t="s">
+      <c r="A72" s="8"/>
+      <c r="B72" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="31"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D73" s="5"/>
-      <c r="E73" s="10"/>
-      <c r="F73" t="s">
+      <c r="B73" s="8"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="30" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="10"/>
-      <c r="F74" t="s">
+      <c r="B74" s="8"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="30" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="10"/>
-      <c r="F75" t="s">
+      <c r="B75" s="8"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="30" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="10"/>
-      <c r="F76" t="s">
+      <c r="B76" s="8"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="30" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F8:F9"/>
     <mergeCell ref="E62:E76"/>
-    <mergeCell ref="G32:G36"/>
-    <mergeCell ref="E11:E17"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="F11:F17"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="F18:F21"/>
     <mergeCell ref="F68:F72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Outline" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -106,12 +106,6 @@
     <t>Sammeln</t>
   </si>
   <si>
-    <t>(Gabor)?</t>
-  </si>
-  <si>
-    <t>(Gabor) ?</t>
-  </si>
-  <si>
     <t>hlrs</t>
   </si>
   <si>
@@ -175,9 +169,6 @@
     <t>5.3 Monte Carlo</t>
   </si>
   <si>
-    <t>5.3.1 Moves</t>
-  </si>
-  <si>
     <t>5.3.2 Resize</t>
   </si>
   <si>
@@ -311,6 +302,12 @@
   </si>
   <si>
     <t>Stand</t>
+  </si>
+  <si>
+    <t>Gabor</t>
+  </si>
+  <si>
+    <t>5.3.1 Translation and rotation</t>
   </si>
 </sst>
 </file>
@@ -423,9 +420,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -458,22 +452,25 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -786,60 +783,60 @@
     <col min="2" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="20" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+    <row r="2" spans="1:9" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="24"/>
+        <v>44</v>
+      </c>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="24"/>
+        <v>45</v>
+      </c>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="25"/>
+      <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -847,15 +844,15 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>32</v>
+      <c r="F8" s="27" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -866,7 +863,7 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="27" t="s">
         <v>20</v>
       </c>
     </row>
@@ -874,43 +871,43 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="24"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="24"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="24"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="24"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="24"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="24"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="27" t="s">
         <v>21</v>
       </c>
     </row>
@@ -918,19 +915,19 @@
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="24"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="24"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="24"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -940,119 +937,119 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="24"/>
+        <v>48</v>
+      </c>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="24"/>
+        <v>49</v>
+      </c>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="24"/>
+        <v>97</v>
+      </c>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="24"/>
+        <v>51</v>
+      </c>
+      <c r="F29" s="27"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="30" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F33" s="27"/>
+        <v>55</v>
+      </c>
+      <c r="F33" s="30"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="27"/>
+        <v>56</v>
+      </c>
+      <c r="F34" s="30"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F35" s="27"/>
+        <v>57</v>
+      </c>
+      <c r="F35" s="30"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="27"/>
+        <v>58</v>
+      </c>
+      <c r="F36" s="30"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="24" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14" t="s">
-        <v>64</v>
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="25" t="s">
         <v>27</v>
       </c>
       <c r="G39" s="4"/>
@@ -1062,14 +1059,14 @@
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14" t="s">
-        <v>65</v>
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G40" s="4"/>
@@ -1079,14 +1076,14 @@
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14" t="s">
-        <v>66</v>
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="4"/>
@@ -1096,14 +1093,14 @@
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14" t="s">
-        <v>67</v>
+      <c r="A42" s="12"/>
+      <c r="B42" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="28" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="4"/>
@@ -1113,14 +1110,14 @@
       <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14" t="s">
-        <v>68</v>
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="29"/>
+      <c r="F43" s="28"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -1128,14 +1125,14 @@
       <c r="K43" s="4"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="s">
-        <v>69</v>
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="29"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -1143,14 +1140,14 @@
       <c r="K44" s="4"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14" t="s">
-        <v>73</v>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="28"/>
+      <c r="F45" s="25"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -1158,14 +1155,14 @@
       <c r="K45" s="4"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14" t="s">
-        <v>72</v>
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="28" t="s">
+      <c r="F46" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="4"/>
@@ -1175,15 +1172,15 @@
       <c r="K46" s="4"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14" t="s">
-        <v>71</v>
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="28" t="s">
-        <v>31</v>
+      <c r="F47" s="25" t="s">
+        <v>96</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1192,15 +1189,15 @@
       <c r="K47" s="4"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="s">
-        <v>70</v>
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="28" t="s">
-        <v>31</v>
+      <c r="F48" s="25" t="s">
+        <v>96</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -1209,14 +1206,14 @@
       <c r="K48" s="4"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14" t="s">
-        <v>74</v>
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="25" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="4"/>
@@ -1226,15 +1223,15 @@
       <c r="K49" s="4"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="s">
-        <v>75</v>
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="28" t="s">
-        <v>94</v>
+      <c r="F50" s="25" t="s">
+        <v>91</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -1243,14 +1240,14 @@
       <c r="K50" s="4"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="15" t="s">
-        <v>76</v>
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="28"/>
+      <c r="F51" s="25"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -1258,14 +1255,14 @@
       <c r="K51" s="4"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="14" t="s">
-        <v>77</v>
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="28"/>
+      <c r="F52" s="25"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -1273,14 +1270,14 @@
       <c r="K52" s="4"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14" t="s">
-        <v>78</v>
+      <c r="A53" s="12"/>
+      <c r="B53" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="25" t="s">
         <v>21</v>
       </c>
       <c r="G53" s="4"/>
@@ -1290,14 +1287,14 @@
       <c r="K53" s="4"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14" t="s">
-        <v>95</v>
+      <c r="A54" s="12"/>
+      <c r="B54" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="28"/>
+      <c r="F54" s="25"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -1305,14 +1302,14 @@
       <c r="K54" s="4"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="14" t="s">
-        <v>79</v>
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="28" t="s">
+      <c r="F55" s="25" t="s">
         <v>28</v>
       </c>
       <c r="G55" s="4"/>
@@ -1322,15 +1319,15 @@
       <c r="K55" s="4"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="14" t="s">
-        <v>80</v>
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="28" t="s">
-        <v>93</v>
+      <c r="F56" s="25" t="s">
+        <v>90</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -1339,18 +1336,18 @@
       <c r="K56" s="4"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="16" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -1358,15 +1355,15 @@
       <c r="K57" s="4"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="14" t="s">
-        <v>81</v>
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="28" t="s">
-        <v>33</v>
+      <c r="F58" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -1375,15 +1372,15 @@
       <c r="K58" s="4"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="17" t="s">
-        <v>82</v>
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="28" t="s">
-        <v>33</v>
+      <c r="F59" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -1392,17 +1389,17 @@
       <c r="K59" s="4"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>37</v>
+      <c r="A60" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="19"/>
+      <c r="D60" s="18"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="28" t="s">
-        <v>44</v>
+      <c r="F60" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -1412,150 +1409,150 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D61" s="5"/>
-      <c r="F61" s="25"/>
+      <c r="F61" s="23"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="F62" s="30"/>
+      <c r="F62" s="26"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="30"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="26"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="10"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="30"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="26"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7"/>
       <c r="B65" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="10"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="30"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="26"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7"/>
       <c r="B66" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="10"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="30" t="s">
-        <v>42</v>
+      <c r="E66" s="29"/>
+      <c r="F66" s="26" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
       <c r="D67" s="10"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="30"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="26"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="8"/>
-      <c r="B68" s="12" t="s">
-        <v>86</v>
+      <c r="B68" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="10"/>
-      <c r="E68" s="11"/>
+      <c r="E68" s="29"/>
       <c r="F68" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>
-      <c r="B69" s="12" t="s">
-        <v>87</v>
+      <c r="B69" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="10"/>
-      <c r="E69" s="11"/>
+      <c r="E69" s="29"/>
       <c r="F69" s="31"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="8"/>
-      <c r="B70" s="12" t="s">
-        <v>88</v>
+      <c r="B70" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="10"/>
-      <c r="E70" s="11"/>
+      <c r="E70" s="29"/>
       <c r="F70" s="31"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="8"/>
-      <c r="B71" s="12" t="s">
-        <v>89</v>
+      <c r="B71" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="10"/>
-      <c r="E71" s="11"/>
+      <c r="E71" s="29"/>
       <c r="F71" s="31"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="8"/>
-      <c r="B72" s="12" t="s">
-        <v>90</v>
+      <c r="B72" s="11" t="s">
+        <v>87</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="10"/>
-      <c r="E72" s="11"/>
+      <c r="E72" s="29"/>
       <c r="F72" s="31"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="9"/>
       <c r="D73" s="10"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="30" t="s">
-        <v>96</v>
+      <c r="E73" s="29"/>
+      <c r="F73" s="26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="9"/>
       <c r="D74" s="10"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="30" t="s">
+      <c r="E74" s="29"/>
+      <c r="F74" s="26" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1566,20 +1563,20 @@
       <c r="B75" s="8"/>
       <c r="C75" s="9"/>
       <c r="D75" s="10"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="30" t="s">
+      <c r="E75" s="29"/>
+      <c r="F75" s="26" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="9"/>
       <c r="D76" s="10"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="30" t="s">
+      <c r="E76" s="29"/>
+      <c r="F76" s="26" t="s">
         <v>20</v>
       </c>
     </row>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -88,12 +88,6 @@
     <t>later</t>
   </si>
   <si>
-    <t>Tatjana</t>
-  </si>
-  <si>
-    <t>Andreas + Gabor</t>
-  </si>
-  <si>
     <t>Alle</t>
   </si>
   <si>
@@ -175,87 +169,6 @@
     <t>5.4 Simulation Setup</t>
   </si>
   <si>
-    <t>5.5 Ensembles</t>
-  </si>
-  <si>
-    <t>5.5.1 multiple Ensembles for multiple state points</t>
-  </si>
-  <si>
-    <t>5.5.2 Micro-Canonical Ensemble (NVE)</t>
-  </si>
-  <si>
-    <t>5.5.3 Canonical Ensemble (NVT)</t>
-  </si>
-  <si>
-    <t>5.5.4 Isobaric-isothermal Ensemble (NpT)</t>
-  </si>
-  <si>
-    <t>5.5.5 Grand-canonical Method (?VT)</t>
-  </si>
-  <si>
-    <t>5.6 Interaction-Types</t>
-  </si>
-  <si>
-    <t>5.6.1 Dispersive and Repulsive Interaction</t>
-  </si>
-  <si>
-    <t>5.6.2 Electrostatic Interaction</t>
-  </si>
-  <si>
-    <t>5.6.3 Intramolecular Interactions</t>
-  </si>
-  <si>
-    <t>5.6.4 Mixing rules</t>
-  </si>
-  <si>
-    <t>5.7 cutoff &amp; long range correction</t>
-  </si>
-  <si>
-    <t>5.7.1 Reaction Field</t>
-  </si>
-  <si>
-    <t>5.7.2 Ewald Summation</t>
-  </si>
-  <si>
-    <t>5.8.3 sectond derivatives</t>
-  </si>
-  <si>
-    <t>5.8.2 caloric properties</t>
-  </si>
-  <si>
-    <t>5.8.1 thermal properties</t>
-  </si>
-  <si>
-    <t>5.8 Computing physical properties</t>
-  </si>
-  <si>
-    <t>5.8.4 transport properties</t>
-  </si>
-  <si>
-    <t>5.8.5 configurational properties</t>
-  </si>
-  <si>
-    <t>5.8.6 Henry' s law Constant</t>
-  </si>
-  <si>
-    <t>5.8.7 second virial coefficient</t>
-  </si>
-  <si>
-    <t>5.9 statistical Errors</t>
-  </si>
-  <si>
-    <t>5.10.1 Vapor-Liquid equilibrium</t>
-  </si>
-  <si>
-    <t>5.10.2 osmotic pressure</t>
-  </si>
-  <si>
-    <t>5.10.3 humid air Ensemble</t>
-  </si>
-  <si>
-    <t>5.10.4 MCOR</t>
-  </si>
-  <si>
     <t>7.4 Benchmarks/ Test case</t>
   </si>
   <si>
@@ -289,12 +202,6 @@
     <t>Max</t>
   </si>
   <si>
-    <t>Tatjana / Simon</t>
-  </si>
-  <si>
-    <t>5.10 Special Features</t>
-  </si>
-  <si>
     <t>Andreas / Simon</t>
   </si>
   <si>
@@ -308,6 +215,81 @@
   </si>
   <si>
     <t>5.3.1 Translation and rotation</t>
+  </si>
+  <si>
+    <t>5.5 Interaction-Types</t>
+  </si>
+  <si>
+    <t>5.5.1 Dispersive and Repulsive Interaction</t>
+  </si>
+  <si>
+    <t>5.5.2 Electrostatic Interaction</t>
+  </si>
+  <si>
+    <t>5.5.3 Intramolecular Interactions</t>
+  </si>
+  <si>
+    <t>5.5.4 Mixing rules</t>
+  </si>
+  <si>
+    <t>5.6 cutoff &amp; long range correction</t>
+  </si>
+  <si>
+    <t>5.6.1 Reaction Field</t>
+  </si>
+  <si>
+    <t>5.6.2 Ewald Summation</t>
+  </si>
+  <si>
+    <t>5.7 Computing physical properties</t>
+  </si>
+  <si>
+    <t>5.7.1 Ensembles Overview</t>
+  </si>
+  <si>
+    <t>5.7.2 statistical errors (block averaging method according to Flyvbjerg and Petersen) Gabor</t>
+  </si>
+  <si>
+    <t>5.7.3 static properties from helmholtz free energy derivatives (NVT, NVE) Gabor</t>
+  </si>
+  <si>
+    <t>5.7.4 static properties from conventional fluctuation formulas (NpT, NpH) Gabor</t>
+  </si>
+  <si>
+    <t>5.7.4 transport properties (NVT, NVE) Tatjana</t>
+  </si>
+  <si>
+    <t>5.7.6 radial distribution function            Tatjana / Simon</t>
+  </si>
+  <si>
+    <t>5.7.7 Henry' s law Constant Andreas    Andreas+Gabor</t>
+  </si>
+  <si>
+    <t>5.7.8 second virial coefficient               Andreas+Gabor</t>
+  </si>
+  <si>
+    <t>5.7.9 chemical potential and partial molar properties Andreas+Gabor</t>
+  </si>
+  <si>
+    <t>5.8 statistical Errors</t>
+  </si>
+  <si>
+    <t>5.9 Special Features</t>
+  </si>
+  <si>
+    <t>5.9.1 Vapor-Liquid equilibrium</t>
+  </si>
+  <si>
+    <t>5.9.2 osmotic pressure</t>
+  </si>
+  <si>
+    <t>5.9.3 humid air Ensemble</t>
+  </si>
+  <si>
+    <t>5.9.4 MCOR</t>
+  </si>
+  <si>
+    <t>5.9.5 multiple Ensembles for multiple state points</t>
   </si>
 </sst>
 </file>
@@ -396,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -425,9 +407,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -468,9 +447,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -776,67 +752,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K76"/>
+  <dimension ref="A2:K73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
+    <row r="2" spans="1:9" s="18" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="27"/>
+        <v>42</v>
+      </c>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="27"/>
+        <v>43</v>
+      </c>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="23"/>
+      <c r="F6" s="22"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -844,15 +820,15 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>30</v>
+      <c r="F8" s="26" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="27"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -863,7 +839,7 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -871,43 +847,43 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="27"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="27"/>
+      <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="27"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="27"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="27"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="27"/>
+      <c r="F17" s="26"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>21</v>
       </c>
     </row>
@@ -915,19 +891,19 @@
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="27"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="27"/>
+      <c r="F20" s="26"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="27"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -937,121 +913,174 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="27"/>
+        <v>46</v>
+      </c>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="27"/>
+        <v>47</v>
+      </c>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>96</v>
+        <v>48</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F28" s="27"/>
+        <v>66</v>
+      </c>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F29" s="27"/>
+        <v>49</v>
+      </c>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="30"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="30"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="30"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="30"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>27</v>
-      </c>
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13" t="s">
-        <v>61</v>
-      </c>
+      <c r="B39" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="25" t="s">
-        <v>27</v>
-      </c>
+      <c r="F39" s="24"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -1060,15 +1089,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="13" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="25" t="s">
-        <v>22</v>
-      </c>
+      <c r="F40" s="24"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -1077,15 +1104,13 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="13" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="25" t="s">
-        <v>20</v>
-      </c>
+      <c r="F41" s="24"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -1094,15 +1119,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
-      <c r="B42" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="4"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="28" t="s">
-        <v>21</v>
-      </c>
+      <c r="F42" s="24"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -1111,13 +1134,13 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
+      <c r="B43" s="13"/>
       <c r="C43" s="13" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="28"/>
+      <c r="F43" s="24"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -1126,13 +1149,13 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
+      <c r="B44" s="13"/>
       <c r="C44" s="13" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="28"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -1141,13 +1164,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
-      <c r="B45" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="4"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="25"/>
+      <c r="F45" s="24"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -1156,15 +1179,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
+      <c r="B46" s="13"/>
       <c r="C46" s="13" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="25" t="s">
-        <v>22</v>
-      </c>
+      <c r="F46" s="24"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -1173,15 +1194,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
+      <c r="B47" s="13"/>
       <c r="C47" s="13" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="F47" s="24"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -1190,15 +1209,13 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
+      <c r="B48" s="13"/>
       <c r="C48" s="13" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="25" t="s">
-        <v>96</v>
-      </c>
+      <c r="F48" s="24"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -1207,14 +1224,14 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13" t="s">
-        <v>71</v>
-      </c>
+      <c r="B49" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="25" t="s">
-        <v>24</v>
+      <c r="F49" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -1224,15 +1241,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13" t="s">
-        <v>72</v>
-      </c>
+      <c r="B50" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="25" t="s">
-        <v>91</v>
-      </c>
+      <c r="F50" s="24"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -1242,12 +1257,14 @@
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
-      <c r="C51" s="14" t="s">
-        <v>73</v>
+      <c r="C51" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="25"/>
+      <c r="F51" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -1258,11 +1275,13 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="13" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="25"/>
+      <c r="F52" s="24" t="s">
+        <v>61</v>
+      </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -1271,16 +1290,18 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
-      <c r="B53" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="4"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" s="4"/>
+      <c r="F53" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -1288,13 +1309,15 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
-      <c r="B54" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="4"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="25"/>
+      <c r="F54" s="24" t="s">
+        <v>29</v>
+      </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -1304,13 +1327,13 @@
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
-      <c r="C55" s="13" t="s">
-        <v>76</v>
+      <c r="C55" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="25" t="s">
-        <v>28</v>
+      <c r="F55" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -1321,14 +1344,12 @@
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
-      <c r="C56" s="13" t="s">
-        <v>77</v>
+      <c r="C56" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="25" t="s">
-        <v>90</v>
-      </c>
+      <c r="F56" s="24"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -1336,262 +1357,208 @@
       <c r="K56" s="4"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" s="4"/>
+      <c r="A57" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="17"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="F57" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
+      <c r="A58" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="F58" s="22"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
+      <c r="A59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="25"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C60" s="4"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="25"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="F61" s="23"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="25"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="A62" s="7"/>
       <c r="B62" s="8" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F62" s="26"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="25"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="7"/>
       <c r="B63" s="8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="26"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="25" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8" t="s">
-        <v>39</v>
-      </c>
+      <c r="A64" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="8"/>
       <c r="C64" s="9"/>
       <c r="D64" s="10"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="26"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="25"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8" t="s">
-        <v>80</v>
+      <c r="A65" s="8"/>
+      <c r="B65" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="10"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="26"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8" t="s">
-        <v>81</v>
+      <c r="A66" s="8"/>
+      <c r="B66" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="10"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="26" t="s">
-        <v>40</v>
-      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="29"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B67" s="8"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="C67" s="9"/>
       <c r="D67" s="10"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="26"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="8"/>
       <c r="B68" s="11" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="10"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="31" t="s">
-        <v>27</v>
-      </c>
+      <c r="E68" s="28"/>
+      <c r="F68" s="29"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>
       <c r="B69" s="11" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="10"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="31"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="29"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="A70" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" s="8"/>
       <c r="C70" s="9"/>
       <c r="D70" s="10"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="31"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="25" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="8"/>
-      <c r="B71" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="A71" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B71" s="8"/>
       <c r="C71" s="9"/>
       <c r="D71" s="10"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="31"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="25" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="8"/>
-      <c r="B72" s="11" t="s">
-        <v>87</v>
-      </c>
+      <c r="A72" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="8"/>
       <c r="C72" s="9"/>
       <c r="D72" s="10"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="31"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="25" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="9"/>
       <c r="D73" s="10"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="26" t="s">
+      <c r="E73" s="28"/>
+      <c r="F73" s="25" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="E62:E76"/>
-    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="E59:E73"/>
     <mergeCell ref="F11:F17"/>
     <mergeCell ref="F24:F26"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F68:F72"/>
+    <mergeCell ref="F65:F69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -271,25 +271,22 @@
     <t>5.7.9 chemical potential and partial molar properties Andreas+Gabor</t>
   </si>
   <si>
-    <t>5.8 statistical Errors</t>
-  </si>
-  <si>
-    <t>5.9 Special Features</t>
-  </si>
-  <si>
-    <t>5.9.1 Vapor-Liquid equilibrium</t>
-  </si>
-  <si>
-    <t>5.9.2 osmotic pressure</t>
-  </si>
-  <si>
-    <t>5.9.3 humid air Ensemble</t>
-  </si>
-  <si>
-    <t>5.9.4 MCOR</t>
-  </si>
-  <si>
-    <t>5.9.5 multiple Ensembles for multiple state points</t>
+    <t>5.8.1 Vapor-Liquid equilibrium</t>
+  </si>
+  <si>
+    <t>5.8.2 osmotic pressure</t>
+  </si>
+  <si>
+    <t>5.8.3 humid air Ensemble</t>
+  </si>
+  <si>
+    <t>5.8.4 MCOR</t>
+  </si>
+  <si>
+    <t>5.8.5 multiple Ensembles for multiple state points</t>
+  </si>
+  <si>
+    <t>5.8 Special Features</t>
   </si>
 </sst>
 </file>
@@ -752,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K73"/>
+  <dimension ref="A2:K72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" customWidth="1"/>
@@ -1225,14 +1222,12 @@
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="24" t="s">
-        <v>21</v>
-      </c>
+      <c r="F49" s="24"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -1241,13 +1236,15 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
-      <c r="B50" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="4"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13" t="s">
+        <v>85</v>
+      </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="24"/>
+      <c r="F50" s="24" t="s">
+        <v>26</v>
+      </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -1258,12 +1255,12 @@
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="24" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1274,15 +1271,17 @@
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
-      <c r="C52" s="13" t="s">
-        <v>88</v>
+      <c r="C52" s="14" t="s">
+        <v>18</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -1291,17 +1290,15 @@
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
-      <c r="C53" s="14" t="s">
-        <v>18</v>
+      <c r="C53" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -1310,8 +1307,8 @@
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
-      <c r="C54" s="13" t="s">
-        <v>89</v>
+      <c r="C54" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -1328,13 +1325,11 @@
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="24" t="s">
-        <v>29</v>
-      </c>
+      <c r="F55" s="24"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -1342,14 +1337,18 @@
       <c r="K55" s="4"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="4"/>
+      <c r="A56" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="17"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="24"/>
+      <c r="F56" s="24" t="s">
+        <v>40</v>
+      </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -1357,49 +1356,40 @@
       <c r="K56" s="4"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="F57" s="22"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="F58" s="22"/>
+      <c r="A58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="25"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A59" s="7"/>
       <c r="B59" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="10"/>
-      <c r="E59" s="28" t="s">
-        <v>23</v>
-      </c>
+      <c r="E59" s="28"/>
       <c r="F59" s="25"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="7"/>
       <c r="B60" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="10"/>
@@ -1409,7 +1399,7 @@
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="7"/>
       <c r="B61" s="8" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="10"/>
@@ -1419,51 +1409,51 @@
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="7"/>
       <c r="B62" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
       <c r="E62" s="28"/>
-      <c r="F62" s="25"/>
+      <c r="F62" s="25" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8" t="s">
-        <v>52</v>
-      </c>
+      <c r="A63" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="8"/>
       <c r="C63" s="9"/>
       <c r="D63" s="10"/>
       <c r="E63" s="28"/>
-      <c r="F63" s="25" t="s">
-        <v>38</v>
-      </c>
+      <c r="F63" s="25"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B64" s="8"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="C64" s="9"/>
       <c r="D64" s="10"/>
       <c r="E64" s="28"/>
-      <c r="F64" s="25"/>
+      <c r="F64" s="29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>
       <c r="B65" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="10"/>
       <c r="E65" s="28"/>
-      <c r="F65" s="29" t="s">
-        <v>25</v>
-      </c>
+      <c r="F65" s="29"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="8"/>
       <c r="B66" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="10"/>
@@ -1473,7 +1463,7 @@
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
       <c r="B67" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="10"/>
@@ -1483,7 +1473,7 @@
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="8"/>
       <c r="B68" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="10"/>
@@ -1491,60 +1481,50 @@
       <c r="F68" s="29"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="8"/>
-      <c r="B69" s="11" t="s">
-        <v>58</v>
-      </c>
+      <c r="A69" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="8"/>
       <c r="C69" s="9"/>
       <c r="D69" s="10"/>
       <c r="E69" s="28"/>
-      <c r="F69" s="29"/>
+      <c r="F69" s="25" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="9"/>
       <c r="D70" s="10"/>
       <c r="E70" s="28"/>
       <c r="F70" s="25" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="9"/>
       <c r="D71" s="10"/>
       <c r="E71" s="28"/>
       <c r="F71" s="25" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="9"/>
       <c r="D72" s="10"/>
       <c r="E72" s="28"/>
       <c r="F72" s="25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1553,12 +1533,12 @@
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="F36:F38"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="E59:E73"/>
+    <mergeCell ref="E58:E72"/>
     <mergeCell ref="F11:F17"/>
     <mergeCell ref="F24:F26"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="F64:F68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>5.8 Special Features</t>
+  </si>
+  <si>
+    <t>Entwurf</t>
+  </si>
+  <si>
+    <t>fertig</t>
   </si>
 </sst>
 </file>
@@ -870,13 +876,13 @@
       </c>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="26"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -884,30 +890,30 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="26"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="26"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="26"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>44</v>
@@ -916,7 +922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
@@ -924,19 +930,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F25" s="26"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F26" s="26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
@@ -944,19 +950,19 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F28" s="26"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F29" s="26"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>50</v>
       </c>
@@ -964,17 +970,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
         <v>68</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -988,7 +997,9 @@
       <c r="F33" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G33" s="4"/>
+      <c r="G33" t="s">
+        <v>91</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1279,10 +1290,12 @@
       <c r="F52" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" t="s">
+        <v>92</v>
+      </c>
+      <c r="H52" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Outline" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -85,24 +85,15 @@
     <t>Michael</t>
   </si>
   <si>
-    <t>later</t>
-  </si>
-  <si>
     <t>Alle</t>
   </si>
   <si>
-    <t>Minh</t>
-  </si>
-  <si>
     <t>Andreas</t>
   </si>
   <si>
     <t>Sammeln</t>
   </si>
   <si>
-    <t>hlrs</t>
-  </si>
-  <si>
     <t>Jadran / Simon</t>
   </si>
   <si>
@@ -130,12 +121,6 @@
     <t>7.3 Vectorization &amp; Memory</t>
   </si>
   <si>
-    <t>Michael ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------</t>
-  </si>
-  <si>
     <t>Simon / Jadran</t>
   </si>
   <si>
@@ -247,30 +232,6 @@
     <t>5.7.1 Ensembles Overview</t>
   </si>
   <si>
-    <t>5.7.2 statistical errors (block averaging method according to Flyvbjerg and Petersen) Gabor</t>
-  </si>
-  <si>
-    <t>5.7.3 static properties from helmholtz free energy derivatives (NVT, NVE) Gabor</t>
-  </si>
-  <si>
-    <t>5.7.4 static properties from conventional fluctuation formulas (NpT, NpH) Gabor</t>
-  </si>
-  <si>
-    <t>5.7.4 transport properties (NVT, NVE) Tatjana</t>
-  </si>
-  <si>
-    <t>5.7.6 radial distribution function            Tatjana / Simon</t>
-  </si>
-  <si>
-    <t>5.7.7 Henry' s law Constant Andreas    Andreas+Gabor</t>
-  </si>
-  <si>
-    <t>5.7.8 second virial coefficient               Andreas+Gabor</t>
-  </si>
-  <si>
-    <t>5.7.9 chemical potential and partial molar properties Andreas+Gabor</t>
-  </si>
-  <si>
     <t>5.8.1 Vapor-Liquid equilibrium</t>
   </si>
   <si>
@@ -293,13 +254,61 @@
   </si>
   <si>
     <t>fertig</t>
+  </si>
+  <si>
+    <t>Minh/ Simon</t>
+  </si>
+  <si>
+    <t>Martin B. /michael</t>
+  </si>
+  <si>
+    <t>Tatjana</t>
+  </si>
+  <si>
+    <t>fehlt noch</t>
+  </si>
+  <si>
+    <t>5.7.2 statistical errors (block averaging method according to Flyvbjerg and Petersen)</t>
+  </si>
+  <si>
+    <t>5.7.3 static properties from helmholtz free energy derivatives (NVT, NVE)</t>
+  </si>
+  <si>
+    <t>5.7.4 static properties from conventional fluctuation formulas (NpT, NpH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7.9 chemical potential and partial molar properties </t>
+  </si>
+  <si>
+    <t>Andreas+Gabor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7.6 radial distribution function            </t>
+  </si>
+  <si>
+    <t>Tatjana / Simon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7.7 Henry' s law Constant Andreas    </t>
+  </si>
+  <si>
+    <t>5.7.8 second virial coefficient               </t>
+  </si>
+  <si>
+    <t>Martin B./Simon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7.4 transport properties (NVT, NVE) </t>
+  </si>
+  <si>
+    <t>fertig?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,19 +324,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -381,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -391,43 +387,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -439,19 +415,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,803 +725,750 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K72"/>
+  <dimension ref="A2:I71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="18" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="26"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="26"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="22"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="D7" s="14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="26"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="D11" s="19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="26"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="26"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="26"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D14" s="19"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="26"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="19"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="26"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="26"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="D18" s="19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="26"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="26"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="D29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="26"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="26"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="26" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="26"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F29" s="26"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="E34" s="4"/>
-      <c r="F34" s="24" t="s">
-        <v>22</v>
-      </c>
+      <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="4"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>20</v>
+      </c>
       <c r="E35" s="4"/>
-      <c r="F35" s="24" t="s">
-        <v>20</v>
-      </c>
+      <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13" t="s">
-        <v>72</v>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="27" t="s">
-        <v>21</v>
-      </c>
+      <c r="D36" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="4"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="17"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="27"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="4"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="17"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="27"/>
+      <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13" t="s">
-        <v>75</v>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="24"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="4"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="16"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="24"/>
+      <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="4"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="E41" s="4"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="4"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="E42" s="4"/>
-      <c r="F42" s="24"/>
+      <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="4"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="E43" s="4"/>
-      <c r="F43" s="24"/>
+      <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="4"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="E44" s="4"/>
-      <c r="F44" s="24"/>
+      <c r="F44" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="4"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>90</v>
+      </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="24"/>
+      <c r="F45" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" s="4"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="E46" s="4"/>
-      <c r="F46" s="24"/>
+      <c r="F46" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D47" s="4"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="E47" s="4"/>
-      <c r="F47" s="24"/>
+      <c r="F47" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="4"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="E48" s="4"/>
-      <c r="F48" s="24"/>
+      <c r="F48" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13" t="s">
-        <v>90</v>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="24"/>
+      <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="F50" s="4"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="24" t="s">
-        <v>61</v>
-      </c>
+      <c r="F51" s="4"/>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="14" t="s">
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="24" t="s">
+      <c r="D52" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G52" t="s">
-        <v>92</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="E53" s="4"/>
-      <c r="F53" s="24" t="s">
-        <v>29</v>
-      </c>
+      <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="E54" s="4"/>
-      <c r="F54" s="24" t="s">
-        <v>29</v>
-      </c>
+      <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="E55" s="4"/>
-      <c r="F55" s="24"/>
+      <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>33</v>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="17"/>
+      <c r="D56" s="16" t="s">
+        <v>35</v>
+      </c>
       <c r="E56" s="4"/>
-      <c r="F56" s="24" t="s">
-        <v>40</v>
-      </c>
+      <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D57" s="5"/>
-      <c r="F57" s="22"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="18"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="28" t="s">
+      <c r="C59" s="4"/>
+      <c r="D59" s="18"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="18"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="16"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="B63" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="17"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="17"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="B66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="17"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="5"/>
+      <c r="B67" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="17"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F58" s="25"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="25"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="25"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="25"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
-      <c r="B62" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C62" s="9"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="25"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="29" t="s">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="28"/>
-      <c r="F65" s="29"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C66" s="9"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="29"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="29"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C68" s="9"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="29"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="25" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="25" t="s">
+      <c r="B71" s="5"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="16" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="E58:E72"/>
-    <mergeCell ref="F11:F17"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="F64:F68"/>
+    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="D57:D60"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D11:D17"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D18:D21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentation/Inhalt manual.xlsx
+++ b/documentation/Inhalt manual.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="97">
   <si>
     <t>1. Getting Started</t>
   </si>
@@ -100,15 +100,6 @@
     <t>Symbolverzeichnis</t>
   </si>
   <si>
-    <t xml:space="preserve"> -&gt; unter "5.5.5 configurational properties"</t>
-  </si>
-  <si>
-    <t>6.</t>
-  </si>
-  <si>
-    <t>Potential Models in the ms2 distribution</t>
-  </si>
-  <si>
     <t>7. Computational Aspects</t>
   </si>
   <si>
@@ -283,9 +274,6 @@
     <t>Andreas+Gabor</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7.6 radial distribution function            </t>
-  </si>
-  <si>
     <t>Tatjana / Simon</t>
   </si>
   <si>
@@ -301,7 +289,22 @@
     <t xml:space="preserve">5.7.4 transport properties (NVT, NVE) </t>
   </si>
   <si>
-    <t>fertig?</t>
+    <t>aus Pogrammm</t>
+  </si>
+  <si>
+    <t>aus Pogramm</t>
+  </si>
+  <si>
+    <t>6. Potential Models in the ms2 distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7.6 configurational properties </t>
+  </si>
+  <si>
+    <t>Kommentar</t>
+  </si>
+  <si>
+    <t>Erläuterung zur Benutzung fehlt!</t>
   </si>
 </sst>
 </file>
@@ -348,12 +351,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -377,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -403,25 +424,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,21 +770,23 @@
   <cols>
     <col min="1" max="1" width="13.140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="3"/>
-    <col min="3" max="3" width="59.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
-      <c r="D2" s="13" t="s">
-        <v>58</v>
+      <c r="D2" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -752,37 +794,36 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="19"/>
+        <v>34</v>
+      </c>
+      <c r="D4" s="18"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="19"/>
+        <v>35</v>
+      </c>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -790,15 +831,18 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>81</v>
+      <c r="D8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -809,7 +853,7 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -817,63 +861,66 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="19"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="18"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="19"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="19"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="19"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="19"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="19"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -883,90 +930,92 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="19"/>
+        <v>38</v>
+      </c>
+      <c r="D25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" t="s">
-        <v>79</v>
+        <v>40</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="19"/>
+        <v>58</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="25"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="25"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>80</v>
+        <v>60</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>77</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>80</v>
+        <v>61</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -976,9 +1025,9 @@
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>22</v>
       </c>
       <c r="E34" s="4"/>
@@ -990,27 +1039,29 @@
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="23" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="20" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -1020,11 +1071,13 @@
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="17"/>
+        <v>65</v>
+      </c>
+      <c r="D37" s="20"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1032,21 +1085,23 @@
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="17"/>
+        <v>66</v>
+      </c>
+      <c r="D38" s="20"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="16"/>
+      <c r="D39" s="14"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -1057,9 +1112,9 @@
       <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" s="16"/>
+        <v>68</v>
+      </c>
+      <c r="D40" s="14"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -1070,15 +1125,16 @@
       <c r="A41" s="5"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -1087,13 +1143,17 @@
       <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -1102,13 +1162,17 @@
       <c r="A43" s="5"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -1117,14 +1181,16 @@
       <c r="A44" s="5"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F44" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -1134,14 +1200,13 @@
       <c r="A45" s="5"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -1151,14 +1216,16 @@
       <c r="A46" s="5"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F46" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1168,14 +1235,16 @@
       <c r="A47" s="5"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="D47" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F47" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1185,14 +1254,13 @@
       <c r="A48" s="5"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -1201,10 +1269,10 @@
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="16"/>
+      <c r="D49" s="14"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -1215,9 +1283,9 @@
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D50" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>24</v>
       </c>
       <c r="E50" s="4"/>
@@ -1230,13 +1298,15 @@
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -1247,15 +1317,13 @@
       <c r="C52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -1264,9 +1332,9 @@
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D53" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E53" s="4"/>
@@ -1279,9 +1347,9 @@
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="23" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="4"/>
@@ -1294,27 +1362,29 @@
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="B56" s="5"/>
       <c r="C56" s="4"/>
-      <c r="D56" s="16" t="s">
-        <v>35</v>
+      <c r="D56" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -1324,143 +1394,154 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C57" s="4"/>
-      <c r="D57" s="18" t="s">
-        <v>93</v>
+      <c r="D57" s="16" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="9"/>
       <c r="B58" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="18"/>
+      <c r="D58" s="16"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="9"/>
       <c r="B59" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C59" s="4"/>
-      <c r="D59" s="18"/>
+      <c r="D59" s="16"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="9"/>
       <c r="B60" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="18"/>
+      <c r="D60" s="16"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="9"/>
       <c r="B61" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C61" s="4"/>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="4"/>
-      <c r="D62" s="16"/>
+      <c r="D62" s="14"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C63" s="4"/>
-      <c r="D63" s="17" t="s">
-        <v>80</v>
+      <c r="D63" s="23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="17"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D64" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C65" s="4"/>
-      <c r="D65" s="17"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="17"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C67" s="4"/>
-      <c r="D67" s="17"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="4"/>
-      <c r="D68" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="4"/>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="4"/>
-      <c r="D70" s="16" t="s">
+      <c r="D70" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="4"/>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="23" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="D36:D38"/>
@@ -1470,7 +1551,7 @@
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="D18:D21"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>